--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>bit sad</t>
+  </si>
+  <si>
+    <t>all okay</t>
   </si>
 </sst>
 </file>
@@ -2303,26 +2306,48 @@
       </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="18"/>
+      <c r="A20" s="18">
+        <v>46278</v>
+      </c>
       <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="15" t="str">
+      <c r="C20" s="19">
+        <v>20</v>
+      </c>
+      <c r="D20" s="19">
+        <v>200</v>
+      </c>
+      <c r="E20" s="19">
+        <v>30</v>
+      </c>
+      <c r="F20" s="19">
+        <v>0</v>
+      </c>
+      <c r="G20" s="19">
+        <v>0</v>
+      </c>
+      <c r="H20" s="19">
+        <v>400</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>650</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="21"/>
+        <v>790</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M20" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N20" s="21" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>all okay</t>
+  </si>
+  <si>
+    <t>not fine</t>
   </si>
 </sst>
 </file>
@@ -2350,26 +2353,50 @@
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="18"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="18">
+        <v>46279</v>
+      </c>
+      <c r="B21" s="19">
+        <v>470</v>
+      </c>
+      <c r="C21" s="19">
+        <v>23</v>
+      </c>
+      <c r="D21" s="19">
+        <v>34</v>
+      </c>
+      <c r="E21" s="19">
+        <v>23</v>
+      </c>
+      <c r="F21" s="19">
+        <v>250</v>
+      </c>
+      <c r="G21" s="19">
+        <v>5</v>
+      </c>
+      <c r="H21" s="19">
+        <v>340</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="21"/>
+        <v>300</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N21" s="21" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2399,26 +2399,50 @@
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="18"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="18">
+        <v>46280</v>
+      </c>
+      <c r="B22" s="19">
+        <v>480</v>
+      </c>
+      <c r="C22" s="19">
+        <v>12</v>
+      </c>
+      <c r="D22" s="19">
+        <v>60</v>
+      </c>
+      <c r="E22" s="19">
+        <v>100</v>
+      </c>
+      <c r="F22" s="19">
+        <v>300</v>
+      </c>
+      <c r="G22" s="19">
+        <v>5</v>
+      </c>
+      <c r="H22" s="19">
+        <v>400</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1352</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="21"/>
+        <v>88</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N22" s="21" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>not fine</t>
+  </si>
+  <si>
+    <t>okayish</t>
   </si>
 </sst>
 </file>
@@ -2445,26 +2448,50 @@
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="18"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="18">
+        <v>46281</v>
+      </c>
+      <c r="B23" s="19">
+        <v>470</v>
+      </c>
+      <c r="C23" s="19">
+        <v>20</v>
+      </c>
+      <c r="D23" s="19">
+        <v>60</v>
+      </c>
+      <c r="E23" s="19">
+        <v>60</v>
+      </c>
+      <c r="F23" s="19">
+        <v>150</v>
+      </c>
+      <c r="G23" s="19">
+        <v>3</v>
+      </c>
+      <c r="H23" s="19">
+        <v>200</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="21"/>
+        <v>480</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="M23" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N23" s="21" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>okayish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tired </t>
   </si>
 </sst>
 </file>
@@ -2494,26 +2497,50 @@
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="18">
+        <v>46282</v>
+      </c>
+      <c r="B24" s="19">
+        <v>487</v>
+      </c>
+      <c r="C24" s="19">
+        <v>30</v>
+      </c>
+      <c r="D24" s="19">
+        <v>120</v>
+      </c>
+      <c r="E24" s="19">
+        <v>120</v>
+      </c>
+      <c r="F24" s="19">
+        <v>250</v>
+      </c>
+      <c r="G24" s="19">
+        <v>5</v>
+      </c>
+      <c r="H24" s="19">
+        <v>300</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1307</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="21"/>
+        <v>133</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M24" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N24" s="21" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t xml:space="preserve">tired </t>
+  </si>
+  <si>
+    <t>mentally exhausted</t>
   </si>
 </sst>
 </file>
@@ -2543,26 +2546,50 @@
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="18"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="18">
+        <v>46285</v>
+      </c>
+      <c r="B25" s="19">
+        <v>480</v>
+      </c>
+      <c r="C25" s="19">
+        <v>20</v>
+      </c>
+      <c r="D25" s="19">
+        <v>30</v>
+      </c>
+      <c r="E25" s="19">
+        <v>20</v>
+      </c>
+      <c r="F25" s="19">
+        <v>0</v>
+      </c>
+      <c r="G25" s="19">
+        <v>0</v>
+      </c>
+      <c r="H25" s="19">
+        <v>400</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="21"/>
+        <v>490</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M25" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25" s="21" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2592,48 +2592,96 @@
       </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="18"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="18">
+        <v>46283</v>
+      </c>
+      <c r="B26" s="19">
+        <v>470</v>
+      </c>
+      <c r="C26" s="19">
+        <v>30</v>
+      </c>
+      <c r="D26" s="19">
+        <v>30</v>
+      </c>
+      <c r="E26" s="19">
+        <v>10</v>
+      </c>
+      <c r="F26" s="19">
+        <v>0</v>
+      </c>
+      <c r="G26" s="19">
+        <v>0</v>
+      </c>
+      <c r="H26" s="19">
+        <v>360</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="21"/>
+        <v>540</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M26" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N26" s="21" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="18"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="18">
+        <v>46284</v>
+      </c>
+      <c r="B27" s="19">
+        <v>480</v>
+      </c>
+      <c r="C27" s="19">
+        <v>30</v>
+      </c>
+      <c r="D27" s="19">
+        <v>30</v>
+      </c>
+      <c r="E27" s="19">
+        <v>12</v>
+      </c>
+      <c r="F27" s="19">
+        <v>160</v>
+      </c>
+      <c r="G27" s="19">
+        <v>3</v>
+      </c>
+      <c r="H27" s="19">
+        <v>457</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1169</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="21"/>
+        <v>271</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N27" s="21" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,12 @@
   </si>
   <si>
     <t>mentally exhausted</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
   </si>
 </sst>
 </file>
@@ -2684,26 +2690,50 @@
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="18"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="18">
+        <v>46286</v>
+      </c>
+      <c r="B28" s="19">
+        <v>480</v>
+      </c>
+      <c r="C28" s="19">
+        <v>20</v>
+      </c>
+      <c r="D28" s="19">
+        <v>40</v>
+      </c>
+      <c r="E28" s="19">
+        <v>30</v>
+      </c>
+      <c r="F28" s="19">
+        <v>250</v>
+      </c>
+      <c r="G28" s="19">
+        <v>5</v>
+      </c>
+      <c r="H28" s="19">
+        <v>400</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="21"/>
+        <v>220</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="M28" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N28" s="21" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>cheerful day</t>
   </si>
 </sst>
 </file>
@@ -2736,26 +2739,50 @@
       </c>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="18"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="18">
+        <v>46287</v>
+      </c>
+      <c r="B29" s="19">
+        <v>480</v>
+      </c>
+      <c r="C29" s="19">
+        <v>30</v>
+      </c>
+      <c r="D29" s="19">
+        <v>60</v>
+      </c>
+      <c r="E29" s="19">
+        <v>200</v>
+      </c>
+      <c r="F29" s="19">
+        <v>300</v>
+      </c>
+      <c r="G29" s="19">
+        <v>5</v>
+      </c>
+      <c r="H29" s="19">
+        <v>340</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="21"/>
+        <v>30</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M29" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N29" s="21" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2785,26 +2785,50 @@
       </c>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="18"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="18">
+        <v>46288</v>
+      </c>
+      <c r="B30" s="19">
+        <v>470</v>
+      </c>
+      <c r="C30" s="19">
+        <v>10</v>
+      </c>
+      <c r="D30" s="19">
+        <v>55</v>
+      </c>
+      <c r="E30" s="19">
+        <v>120</v>
+      </c>
+      <c r="F30" s="19">
+        <v>250</v>
+      </c>
+      <c r="G30" s="19">
+        <v>6</v>
+      </c>
+      <c r="H30" s="19">
+        <v>450</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1355</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
-      <c r="M30" s="20"/>
-      <c r="N30" s="21"/>
+        <v>85</v>
+      </c>
+      <c r="K30" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="L30" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N30" s="21" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -262,6 +262,18 @@
   </si>
   <si>
     <t>cheerful day</t>
+  </si>
+  <si>
+    <t>grateful</t>
+  </si>
+  <si>
+    <t>happy</t>
+  </si>
+  <si>
+    <t>bit happy</t>
+  </si>
+  <si>
+    <t>all well</t>
   </si>
 </sst>
 </file>
@@ -2831,202 +2843,414 @@
       </c>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="18"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="18">
+        <v>46289</v>
+      </c>
+      <c r="B31" s="19">
+        <v>467</v>
+      </c>
+      <c r="C31" s="19">
+        <v>20</v>
+      </c>
+      <c r="D31" s="19">
+        <v>60</v>
+      </c>
+      <c r="E31" s="19">
+        <v>60</v>
+      </c>
+      <c r="F31" s="19">
+        <v>300</v>
+      </c>
+      <c r="G31" s="19">
+        <v>5</v>
+      </c>
+      <c r="H31" s="19">
+        <v>500</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1407</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="21"/>
+        <v>33</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L31" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M31" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N31" s="21" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="18"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="18">
+        <v>46252</v>
+      </c>
+      <c r="B32" s="19">
+        <v>470</v>
+      </c>
+      <c r="C32" s="19">
+        <v>30</v>
+      </c>
+      <c r="D32" s="19">
+        <v>40</v>
+      </c>
+      <c r="E32" s="19">
+        <v>50</v>
+      </c>
+      <c r="F32" s="19">
+        <v>200</v>
+      </c>
+      <c r="G32" s="19">
+        <v>5</v>
+      </c>
+      <c r="H32" s="19">
+        <v>390</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
-      <c r="M32" s="20"/>
-      <c r="N32" s="21"/>
+        <v>260</v>
+      </c>
+      <c r="K32" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L32" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N32" s="21" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="18"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="18">
+        <v>46253</v>
+      </c>
+      <c r="B33" s="19">
+        <v>480</v>
+      </c>
+      <c r="C33" s="19">
+        <v>40</v>
+      </c>
+      <c r="D33" s="19">
+        <v>50</v>
+      </c>
+      <c r="E33" s="19">
+        <v>67</v>
+      </c>
+      <c r="F33" s="19">
+        <v>260</v>
+      </c>
+      <c r="G33" s="19">
+        <v>5</v>
+      </c>
+      <c r="H33" s="19">
+        <v>300</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1197</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="21"/>
+        <v>243</v>
+      </c>
+      <c r="K33" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L33" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M33" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N33" s="21" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="18"/>
+      <c r="A34" s="18">
+        <v>46254</v>
+      </c>
       <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="15" t="str">
+      <c r="C34" s="19">
+        <v>50</v>
+      </c>
+      <c r="D34" s="19">
+        <v>40</v>
+      </c>
+      <c r="E34" s="19">
+        <v>50</v>
+      </c>
+      <c r="F34" s="19">
+        <v>300</v>
+      </c>
+      <c r="G34" s="19">
+        <v>6</v>
+      </c>
+      <c r="H34" s="19">
+        <v>400</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20"/>
-      <c r="N34" s="21"/>
+        <v>600</v>
+      </c>
+      <c r="K34" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L34" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M34" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N34" s="21" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="18"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="18">
+        <v>46255</v>
+      </c>
+      <c r="B35" s="19">
+        <v>460</v>
+      </c>
+      <c r="C35" s="19">
+        <v>30</v>
+      </c>
+      <c r="D35" s="19">
+        <v>50</v>
+      </c>
+      <c r="E35" s="19">
+        <v>50</v>
+      </c>
+      <c r="F35" s="19">
+        <v>260</v>
+      </c>
+      <c r="G35" s="19">
+        <v>5</v>
+      </c>
+      <c r="H35" s="19">
+        <v>500</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="21"/>
+        <v>90</v>
+      </c>
+      <c r="K35" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L35" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N35" s="21" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="18"/>
+      <c r="A36" s="18">
+        <v>46256</v>
+      </c>
       <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="15" t="str">
+      <c r="C36" s="19">
+        <v>20</v>
+      </c>
+      <c r="D36" s="19">
+        <v>30</v>
+      </c>
+      <c r="E36" s="19">
+        <v>30</v>
+      </c>
+      <c r="F36" s="19">
+        <v>280</v>
+      </c>
+      <c r="G36" s="19">
+        <v>6</v>
+      </c>
+      <c r="H36" s="19">
+        <v>500</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="20"/>
-      <c r="L36" s="20"/>
-      <c r="M36" s="20"/>
-      <c r="N36" s="21"/>
+        <v>580</v>
+      </c>
+      <c r="K36" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="L36" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M36" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N36" s="21" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="18"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="18">
+        <v>46257</v>
+      </c>
+      <c r="B37" s="19">
+        <v>400</v>
+      </c>
+      <c r="C37" s="19">
+        <v>40</v>
+      </c>
+      <c r="D37" s="19">
+        <v>40</v>
+      </c>
+      <c r="E37" s="19">
+        <v>40</v>
+      </c>
+      <c r="F37" s="19">
+        <v>290</v>
+      </c>
+      <c r="G37" s="19">
+        <v>5</v>
+      </c>
+      <c r="H37" s="19">
+        <v>300</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="20"/>
-      <c r="N37" s="21"/>
+        <v>330</v>
+      </c>
+      <c r="K37" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L37" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M37" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N37" s="21" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" s="18"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="18">
+        <v>46258</v>
+      </c>
+      <c r="B38" s="19">
+        <v>480</v>
+      </c>
+      <c r="C38" s="19">
+        <v>40</v>
+      </c>
+      <c r="D38" s="19">
+        <v>30</v>
+      </c>
+      <c r="E38" s="19">
+        <v>40</v>
+      </c>
+      <c r="F38" s="19">
+        <v>480</v>
+      </c>
+      <c r="G38" s="19">
+        <v>6</v>
+      </c>
+      <c r="H38" s="19">
+        <v>200</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="20"/>
-      <c r="L38" s="20"/>
-      <c r="M38" s="20"/>
-      <c r="N38" s="21"/>
+        <v>170</v>
+      </c>
+      <c r="K38" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L38" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M38" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N38" s="21" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="18"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="18">
+        <v>46259</v>
+      </c>
+      <c r="B39" s="19">
+        <v>450</v>
+      </c>
+      <c r="C39" s="19">
+        <v>20</v>
+      </c>
+      <c r="D39" s="19">
+        <v>43</v>
+      </c>
+      <c r="E39" s="19">
+        <v>50</v>
+      </c>
+      <c r="F39" s="19">
+        <v>460</v>
+      </c>
+      <c r="G39" s="19">
+        <v>6</v>
+      </c>
+      <c r="H39" s="19">
+        <v>300</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1323</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="20"/>
-      <c r="L39" s="20"/>
-      <c r="M39" s="20"/>
-      <c r="N39" s="21"/>
+        <v>117</v>
+      </c>
+      <c r="K39" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L39" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M39" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N39" s="21" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3253,26 +3253,50 @@
       </c>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" s="18"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="18">
+        <v>46259</v>
+      </c>
+      <c r="B40" s="19">
+        <v>460</v>
+      </c>
+      <c r="C40" s="19">
+        <v>30</v>
+      </c>
+      <c r="D40" s="19">
+        <v>200</v>
+      </c>
+      <c r="E40" s="19">
+        <v>20</v>
+      </c>
+      <c r="F40" s="19">
+        <v>150</v>
+      </c>
+      <c r="G40" s="19">
+        <v>3</v>
+      </c>
+      <c r="H40" s="19">
+        <v>250</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="20"/>
-      <c r="L40" s="20"/>
-      <c r="M40" s="20"/>
-      <c r="N40" s="21"/>
+        <v>330</v>
+      </c>
+      <c r="K40" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L40" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M40" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N40" s="21" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3299,26 +3299,50 @@
       </c>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="18"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="18">
+        <v>46260</v>
+      </c>
+      <c r="B41" s="19">
+        <v>470</v>
+      </c>
+      <c r="C41" s="19">
+        <v>20</v>
+      </c>
+      <c r="D41" s="19">
+        <v>60</v>
+      </c>
+      <c r="E41" s="19">
+        <v>200</v>
+      </c>
+      <c r="F41" s="19">
+        <v>0</v>
+      </c>
+      <c r="G41" s="19">
+        <v>0</v>
+      </c>
+      <c r="H41" s="19">
+        <v>540</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="20"/>
-      <c r="L41" s="20"/>
-      <c r="M41" s="20"/>
-      <c r="N41" s="21"/>
+        <v>150</v>
+      </c>
+      <c r="K41" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L41" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M41" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N41" s="21" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="18"/>
@@ -4336,18 +4360,21 @@
       <c r="A88" s="18"/>
       <c r="B88" s="19"/>
       <c r="C88" s="19"/>
-      <c r="D88" s="19"/>
+      <c r="D88" s="19">
+        <f>AVERAGEIFS(E:E,A:A,"&gt;="&amp;DATE(2026,8,17),A:A,"&lt;="&amp;DATE(2026,9,21))</f>
+        <v>42.3636363636364</v>
+      </c>
       <c r="E88" s="19"/>
       <c r="F88" s="19"/>
       <c r="G88" s="19"/>
       <c r="H88" s="19"/>
-      <c r="I88" s="15" t="str">
+      <c r="I88" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J88" s="15" t="str">
+        <v>42.3636363636364</v>
+      </c>
+      <c r="J88" s="15">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1397.63636363636</v>
       </c>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -4385,14 +4412,8 @@
       <c r="F90" s="19"/>
       <c r="G90" s="19"/>
       <c r="H90" s="19"/>
-      <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="I90" s="15"/>
+      <c r="J90" s="15"/>
       <c r="K90" s="20"/>
       <c r="L90" s="20"/>
       <c r="M90" s="20"/>
@@ -4437,7 +4458,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K92" s="20"/>
+      <c r="K92" s="20">
+        <f>AVERAGEIFS(E:E,A:A,"&gt;="&amp;DATE(2026,8,17),A:A,"&lt;="&amp;DATE(2026,9,21))</f>
+        <v>42.3636363636364</v>
+      </c>
       <c r="L92" s="20"/>
       <c r="M92" s="20"/>
       <c r="N92" s="21"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>all well</t>
+  </si>
+  <si>
+    <t>exhausted</t>
   </si>
 </sst>
 </file>
@@ -3345,70 +3348,142 @@
       </c>
     </row>
     <row r="42" spans="1:14">
-      <c r="A42" s="18"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="18">
+        <v>46261</v>
+      </c>
+      <c r="B42" s="19">
+        <v>478</v>
+      </c>
+      <c r="C42" s="19">
+        <v>25</v>
+      </c>
+      <c r="D42" s="19">
+        <v>120</v>
+      </c>
+      <c r="E42" s="19">
+        <v>49</v>
+      </c>
+      <c r="F42" s="19">
+        <v>0</v>
+      </c>
+      <c r="G42" s="19">
+        <v>0</v>
+      </c>
+      <c r="H42" s="19">
+        <v>400</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1072</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="20"/>
-      <c r="L42" s="20"/>
-      <c r="M42" s="20"/>
-      <c r="N42" s="21"/>
+        <v>368</v>
+      </c>
+      <c r="K42" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L42" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M42" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N42" s="21" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="43" spans="1:14">
-      <c r="A43" s="18"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="18">
+        <v>46262</v>
+      </c>
+      <c r="B43" s="19">
+        <v>450</v>
+      </c>
+      <c r="C43" s="19">
+        <v>10</v>
+      </c>
+      <c r="D43" s="19">
+        <v>40</v>
+      </c>
+      <c r="E43" s="19">
+        <v>120</v>
+      </c>
+      <c r="F43" s="19">
+        <v>0</v>
+      </c>
+      <c r="G43" s="19">
+        <v>0</v>
+      </c>
+      <c r="H43" s="19">
+        <v>430</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="20"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="20"/>
-      <c r="N43" s="21"/>
+        <v>390</v>
+      </c>
+      <c r="K43" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="L43" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M43" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N43" s="21" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="44" spans="1:14">
-      <c r="A44" s="18"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="18">
+        <v>46263</v>
+      </c>
+      <c r="B44" s="19">
+        <v>460</v>
+      </c>
+      <c r="C44" s="19">
+        <v>30</v>
+      </c>
+      <c r="D44" s="19">
+        <v>30</v>
+      </c>
+      <c r="E44" s="19">
+        <v>40</v>
+      </c>
+      <c r="F44" s="19">
+        <v>0</v>
+      </c>
+      <c r="G44" s="19">
+        <v>0</v>
+      </c>
+      <c r="H44" s="19">
+        <v>350</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="20"/>
-      <c r="L44" s="20"/>
-      <c r="M44" s="20"/>
-      <c r="N44" s="21"/>
+        <v>530</v>
+      </c>
+      <c r="K44" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M44" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N44" s="21" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="18"/>
@@ -4362,7 +4437,7 @@
       <c r="C88" s="19"/>
       <c r="D88" s="19">
         <f>AVERAGEIFS(E:E,A:A,"&gt;="&amp;DATE(2026,8,17),A:A,"&lt;="&amp;DATE(2026,9,21))</f>
-        <v>42.3636363636364</v>
+        <v>44.6388888888889</v>
       </c>
       <c r="E88" s="19"/>
       <c r="F88" s="19"/>
@@ -4370,11 +4445,11 @@
       <c r="H88" s="19"/>
       <c r="I88" s="15">
         <f t="shared" si="2"/>
-        <v>42.3636363636364</v>
+        <v>44.6388888888889</v>
       </c>
       <c r="J88" s="15">
         <f t="shared" si="3"/>
-        <v>1397.63636363636</v>
+        <v>1395.36111111111</v>
       </c>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -4460,7 +4535,7 @@
       </c>
       <c r="K92" s="20">
         <f>AVERAGEIFS(E:E,A:A,"&gt;="&amp;DATE(2026,8,17),A:A,"&lt;="&amp;DATE(2026,9,21))</f>
-        <v>42.3636363636364</v>
+        <v>44.6388888888889</v>
       </c>
       <c r="L92" s="20"/>
       <c r="M92" s="20"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -277,6 +277,9 @@
   </si>
   <si>
     <t>exhausted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all well </t>
   </si>
 </sst>
 </file>
@@ -3486,26 +3489,48 @@
       </c>
     </row>
     <row r="45" spans="1:14">
-      <c r="A45" s="18"/>
+      <c r="A45" s="18">
+        <v>46264</v>
+      </c>
       <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="15" t="str">
+      <c r="C45" s="19">
+        <v>20</v>
+      </c>
+      <c r="D45" s="19">
+        <v>90</v>
+      </c>
+      <c r="E45" s="19">
+        <v>30</v>
+      </c>
+      <c r="F45" s="19">
+        <v>0</v>
+      </c>
+      <c r="G45" s="19">
+        <v>0</v>
+      </c>
+      <c r="H45" s="19">
+        <v>350</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>490</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="20"/>
-      <c r="L45" s="20"/>
-      <c r="M45" s="20"/>
-      <c r="N45" s="21"/>
+        <v>950</v>
+      </c>
+      <c r="K45" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L45" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M45" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N45" s="21" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="18"/>
@@ -4437,7 +4462,7 @@
       <c r="C88" s="19"/>
       <c r="D88" s="19">
         <f>AVERAGEIFS(E:E,A:A,"&gt;="&amp;DATE(2026,8,17),A:A,"&lt;="&amp;DATE(2026,9,21))</f>
-        <v>44.6388888888889</v>
+        <v>44.2432432432432</v>
       </c>
       <c r="E88" s="19"/>
       <c r="F88" s="19"/>
@@ -4445,11 +4470,11 @@
       <c r="H88" s="19"/>
       <c r="I88" s="15">
         <f t="shared" si="2"/>
-        <v>44.6388888888889</v>
+        <v>44.2432432432432</v>
       </c>
       <c r="J88" s="15">
         <f t="shared" si="3"/>
-        <v>1395.36111111111</v>
+        <v>1395.75675675676</v>
       </c>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -4535,7 +4560,7 @@
       </c>
       <c r="K92" s="20">
         <f>AVERAGEIFS(E:E,A:A,"&gt;="&amp;DATE(2026,8,17),A:A,"&lt;="&amp;DATE(2026,9,21))</f>
-        <v>44.6388888888889</v>
+        <v>44.2432432432432</v>
       </c>
       <c r="L92" s="20"/>
       <c r="M92" s="20"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="18">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="B41" s="19">
         <v>470</v>
@@ -3352,7 +3352,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="18">
-        <v>46261</v>
+        <v>46292</v>
       </c>
       <c r="B42" s="19">
         <v>478</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="18">
-        <v>46262</v>
+        <v>46293</v>
       </c>
       <c r="B43" s="19">
         <v>450</v>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="18">
-        <v>46263</v>
+        <v>46294</v>
       </c>
       <c r="B44" s="19">
         <v>460</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="18">
-        <v>46264</v>
+        <v>46295</v>
       </c>
       <c r="B45" s="19"/>
       <c r="C45" s="19">
@@ -3533,26 +3533,50 @@
       </c>
     </row>
     <row r="46" spans="1:14">
-      <c r="A46" s="18"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="18">
+        <v>46296</v>
+      </c>
+      <c r="B46" s="19">
+        <v>489</v>
+      </c>
+      <c r="C46" s="19">
+        <v>20</v>
+      </c>
+      <c r="D46" s="19">
+        <v>60</v>
+      </c>
+      <c r="E46" s="19">
+        <v>78</v>
+      </c>
+      <c r="F46" s="19">
+        <v>0</v>
+      </c>
+      <c r="G46" s="19">
+        <v>0</v>
+      </c>
+      <c r="H46" s="19">
+        <v>450</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1097</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="20"/>
-      <c r="L46" s="20"/>
-      <c r="M46" s="20"/>
-      <c r="N46" s="21"/>
+        <v>343</v>
+      </c>
+      <c r="K46" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L46" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M46" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N46" s="21" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="18"/>
@@ -4462,7 +4486,7 @@
       <c r="C88" s="19"/>
       <c r="D88" s="19">
         <f>AVERAGEIFS(E:E,A:A,"&gt;="&amp;DATE(2026,8,17),A:A,"&lt;="&amp;DATE(2026,9,21))</f>
-        <v>44.2432432432432</v>
+        <v>37.4375</v>
       </c>
       <c r="E88" s="19"/>
       <c r="F88" s="19"/>
@@ -4470,11 +4494,11 @@
       <c r="H88" s="19"/>
       <c r="I88" s="15">
         <f t="shared" si="2"/>
-        <v>44.2432432432432</v>
+        <v>37.4375</v>
       </c>
       <c r="J88" s="15">
         <f t="shared" si="3"/>
-        <v>1395.75675675676</v>
+        <v>1402.5625</v>
       </c>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -4560,7 +4584,7 @@
       </c>
       <c r="K92" s="20">
         <f>AVERAGEIFS(E:E,A:A,"&gt;="&amp;DATE(2026,8,17),A:A,"&lt;="&amp;DATE(2026,9,21))</f>
-        <v>44.2432432432432</v>
+        <v>37.4375</v>
       </c>
       <c r="L92" s="20"/>
       <c r="M92" s="20"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3579,26 +3579,48 @@
       </c>
     </row>
     <row r="47" spans="1:14">
-      <c r="A47" s="18"/>
+      <c r="A47" s="18">
+        <v>46297</v>
+      </c>
       <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="15" t="str">
+      <c r="C47" s="19">
+        <v>25</v>
+      </c>
+      <c r="D47" s="19">
+        <v>70</v>
+      </c>
+      <c r="E47" s="19">
+        <v>28</v>
+      </c>
+      <c r="F47" s="19">
+        <v>0</v>
+      </c>
+      <c r="G47" s="19">
+        <v>0</v>
+      </c>
+      <c r="H47" s="19">
+        <v>500</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>623</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="20"/>
-      <c r="L47" s="20"/>
-      <c r="M47" s="20"/>
-      <c r="N47" s="21"/>
+        <v>817</v>
+      </c>
+      <c r="K47" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L47" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M47" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N47" s="21" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3623,26 +3623,50 @@
       </c>
     </row>
     <row r="48" spans="1:14">
-      <c r="A48" s="18"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="18">
+        <v>46298</v>
+      </c>
+      <c r="B48" s="19">
+        <v>460</v>
+      </c>
+      <c r="C48" s="19">
+        <v>20</v>
+      </c>
+      <c r="D48" s="19">
+        <v>60</v>
+      </c>
+      <c r="E48" s="19">
+        <v>32</v>
+      </c>
+      <c r="F48" s="19">
+        <v>0</v>
+      </c>
+      <c r="G48" s="19">
+        <v>0</v>
+      </c>
+      <c r="H48" s="19">
+        <v>459</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1031</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="20"/>
-      <c r="L48" s="20"/>
-      <c r="M48" s="20"/>
-      <c r="N48" s="21"/>
+        <v>409</v>
+      </c>
+      <c r="K48" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="L48" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M48" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N48" s="21" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t xml:space="preserve">all well </t>
+  </si>
+  <si>
+    <t>feeling sad</t>
   </si>
 </sst>
 </file>
@@ -3669,26 +3672,50 @@
       </c>
     </row>
     <row r="49" spans="1:14">
-      <c r="A49" s="18"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="18">
+        <v>46299</v>
+      </c>
+      <c r="B49" s="19">
+        <v>470</v>
+      </c>
+      <c r="C49" s="19">
+        <v>30</v>
+      </c>
+      <c r="D49" s="19">
+        <v>70</v>
+      </c>
+      <c r="E49" s="19">
+        <v>23</v>
+      </c>
+      <c r="F49" s="19">
+        <v>0</v>
+      </c>
+      <c r="G49" s="19">
+        <v>0</v>
+      </c>
+      <c r="H49" s="19">
+        <v>500</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1093</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="20"/>
-      <c r="L49" s="20"/>
-      <c r="M49" s="20"/>
-      <c r="N49" s="21"/>
+        <v>347</v>
+      </c>
+      <c r="K49" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L49" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M49" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N49" s="21" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3718,26 +3718,48 @@
       </c>
     </row>
     <row r="50" spans="1:14">
-      <c r="A50" s="18"/>
+      <c r="A50" s="18">
+        <v>46300</v>
+      </c>
       <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19"/>
-      <c r="I50" s="15" t="str">
+      <c r="C50" s="19">
+        <v>23</v>
+      </c>
+      <c r="D50" s="19">
+        <v>40</v>
+      </c>
+      <c r="E50" s="19">
+        <v>45</v>
+      </c>
+      <c r="F50" s="19">
+        <v>250</v>
+      </c>
+      <c r="G50" s="19">
+        <v>5</v>
+      </c>
+      <c r="H50" s="19">
+        <v>453</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>811</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="20"/>
-      <c r="L50" s="20"/>
-      <c r="M50" s="20"/>
-      <c r="N50" s="21"/>
+        <v>629</v>
+      </c>
+      <c r="K50" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L50" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M50" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N50" s="21" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3762,26 +3762,50 @@
       </c>
     </row>
     <row r="51" spans="1:14">
-      <c r="A51" s="18"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="18">
+        <v>46301</v>
+      </c>
+      <c r="B51" s="19">
+        <v>480</v>
+      </c>
+      <c r="C51" s="19">
+        <v>12</v>
+      </c>
+      <c r="D51" s="19">
+        <v>70</v>
+      </c>
+      <c r="E51" s="19">
+        <v>30</v>
+      </c>
+      <c r="F51" s="19">
+        <v>300</v>
+      </c>
+      <c r="G51" s="19">
+        <v>6</v>
+      </c>
+      <c r="H51" s="19">
+        <v>300</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1192</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="20"/>
-      <c r="L51" s="20"/>
-      <c r="M51" s="20"/>
-      <c r="N51" s="21"/>
+        <v>248</v>
+      </c>
+      <c r="K51" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L51" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M51" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N51" s="21" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t>feeling sad</t>
+  </si>
+  <si>
+    <t>higly stressed</t>
   </si>
 </sst>
 </file>
@@ -3808,26 +3811,50 @@
       </c>
     </row>
     <row r="52" spans="1:14">
-      <c r="A52" s="18"/>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="18">
+        <v>46302</v>
+      </c>
+      <c r="B52" s="19">
+        <v>460</v>
+      </c>
+      <c r="C52" s="19">
+        <v>23</v>
+      </c>
+      <c r="D52" s="19">
+        <v>120</v>
+      </c>
+      <c r="E52" s="19">
+        <v>30</v>
+      </c>
+      <c r="F52" s="19">
+        <v>300</v>
+      </c>
+      <c r="G52" s="19">
+        <v>6</v>
+      </c>
+      <c r="H52" s="19">
+        <v>456</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1389</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="20"/>
-      <c r="L52" s="20"/>
-      <c r="M52" s="20"/>
-      <c r="N52" s="21"/>
+        <v>51</v>
+      </c>
+      <c r="K52" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L52" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="M52" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N52" s="21" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3857,26 +3857,50 @@
       </c>
     </row>
     <row r="53" spans="1:14">
-      <c r="A53" s="18"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="18">
+        <v>46303</v>
+      </c>
+      <c r="B53" s="19">
+        <v>480</v>
+      </c>
+      <c r="C53" s="19">
+        <v>20</v>
+      </c>
+      <c r="D53" s="19">
+        <v>125</v>
+      </c>
+      <c r="E53" s="19">
+        <v>12</v>
+      </c>
+      <c r="F53" s="19">
+        <v>0</v>
+      </c>
+      <c r="G53" s="19">
+        <v>0</v>
+      </c>
+      <c r="H53" s="19">
+        <v>556</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1193</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="20"/>
-      <c r="L53" s="20"/>
-      <c r="M53" s="20"/>
-      <c r="N53" s="21"/>
+        <v>247</v>
+      </c>
+      <c r="K53" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L53" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M53" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N53" s="21" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6300" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>higly stressed</t>
+  </si>
+  <si>
+    <t>fever mode</t>
   </si>
 </sst>
 </file>
@@ -3903,26 +3906,50 @@
       </c>
     </row>
     <row r="54" spans="1:14">
-      <c r="A54" s="18"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="19"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="18">
+        <v>46304</v>
+      </c>
+      <c r="B54" s="19">
+        <v>460</v>
+      </c>
+      <c r="C54" s="19">
+        <v>30</v>
+      </c>
+      <c r="D54" s="19">
+        <v>200</v>
+      </c>
+      <c r="E54" s="19">
+        <v>30</v>
+      </c>
+      <c r="F54" s="19">
+        <v>0</v>
+      </c>
+      <c r="G54" s="19">
+        <v>0</v>
+      </c>
+      <c r="H54" s="19">
+        <v>357</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1077</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="20"/>
-      <c r="L54" s="20"/>
-      <c r="M54" s="20"/>
-      <c r="N54" s="21"/>
+        <v>363</v>
+      </c>
+      <c r="K54" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L54" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M54" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N54" s="21" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6300" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>fever mode</t>
+  </si>
+  <si>
+    <t>having fever</t>
   </si>
 </sst>
 </file>
@@ -3952,26 +3955,50 @@
       </c>
     </row>
     <row r="55" spans="1:14">
-      <c r="A55" s="18"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="19"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="18">
+        <v>46305</v>
+      </c>
+      <c r="B55" s="19">
+        <v>478</v>
+      </c>
+      <c r="C55" s="19">
+        <v>20</v>
+      </c>
+      <c r="D55" s="19">
+        <v>142</v>
+      </c>
+      <c r="E55" s="19">
+        <v>14</v>
+      </c>
+      <c r="F55" s="19">
+        <v>0</v>
+      </c>
+      <c r="G55" s="19">
+        <v>0</v>
+      </c>
+      <c r="H55" s="19">
+        <v>457</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1111</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="20"/>
-      <c r="L55" s="20"/>
-      <c r="M55" s="20"/>
-      <c r="N55" s="21"/>
+        <v>329</v>
+      </c>
+      <c r="K55" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L55" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M55" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N55" s="21" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4001,26 +4001,50 @@
       </c>
     </row>
     <row r="56" spans="1:14">
-      <c r="A56" s="18"/>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="18">
+        <v>46306</v>
+      </c>
+      <c r="B56" s="19">
+        <v>469</v>
+      </c>
+      <c r="C56" s="19">
+        <v>31</v>
+      </c>
+      <c r="D56" s="19">
+        <v>120</v>
+      </c>
+      <c r="E56" s="19">
+        <v>10</v>
+      </c>
+      <c r="F56" s="19">
+        <v>0</v>
+      </c>
+      <c r="G56" s="19">
+        <v>0</v>
+      </c>
+      <c r="H56" s="19">
+        <v>439</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1069</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="20"/>
-      <c r="L56" s="20"/>
-      <c r="M56" s="20"/>
-      <c r="N56" s="21"/>
+        <v>371</v>
+      </c>
+      <c r="K56" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L56" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M56" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N56" s="21" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6300" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4047,26 +4047,50 @@
       </c>
     </row>
     <row r="57" spans="1:14">
-      <c r="A57" s="18"/>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="18">
+        <v>46307</v>
+      </c>
+      <c r="B57" s="19">
+        <v>460</v>
+      </c>
+      <c r="C57" s="19">
+        <v>10</v>
+      </c>
+      <c r="D57" s="19">
+        <v>110</v>
+      </c>
+      <c r="E57" s="19">
+        <v>23</v>
+      </c>
+      <c r="F57" s="19">
+        <v>0</v>
+      </c>
+      <c r="G57" s="19">
+        <v>0</v>
+      </c>
+      <c r="H57" s="19">
+        <v>478</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1081</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="20"/>
-      <c r="L57" s="20"/>
-      <c r="M57" s="20"/>
-      <c r="N57" s="21"/>
+        <v>359</v>
+      </c>
+      <c r="K57" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L57" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M57" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N57" s="21" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6300" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4093,26 +4093,50 @@
       </c>
     </row>
     <row r="58" spans="1:14">
-      <c r="A58" s="18"/>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
-      <c r="F58" s="19"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="19"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="18">
+        <v>46308</v>
+      </c>
+      <c r="B58" s="19">
+        <v>457</v>
+      </c>
+      <c r="C58" s="19">
+        <v>23</v>
+      </c>
+      <c r="D58" s="19">
+        <v>135</v>
+      </c>
+      <c r="E58" s="19">
+        <v>32</v>
+      </c>
+      <c r="F58" s="19">
+        <v>0</v>
+      </c>
+      <c r="G58" s="19">
+        <v>0</v>
+      </c>
+      <c r="H58" s="19">
+        <v>456</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1103</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="20"/>
-      <c r="L58" s="20"/>
-      <c r="M58" s="20"/>
-      <c r="N58" s="21"/>
+        <v>337</v>
+      </c>
+      <c r="K58" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L58" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M58" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N58" s="21" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>having fever</t>
+  </si>
+  <si>
+    <t>irritated</t>
   </si>
 </sst>
 </file>
@@ -4139,26 +4142,48 @@
       </c>
     </row>
     <row r="59" spans="1:14">
-      <c r="A59" s="18"/>
+      <c r="A59" s="18">
+        <v>46309</v>
+      </c>
       <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="19"/>
-      <c r="I59" s="15" t="str">
+      <c r="C59" s="19">
+        <v>21</v>
+      </c>
+      <c r="D59" s="19">
+        <v>140</v>
+      </c>
+      <c r="E59" s="19">
+        <v>23</v>
+      </c>
+      <c r="F59" s="19">
+        <v>0</v>
+      </c>
+      <c r="G59" s="19">
+        <v>0</v>
+      </c>
+      <c r="H59" s="19">
+        <v>470</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>654</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="20"/>
-      <c r="L59" s="20"/>
-      <c r="M59" s="20"/>
-      <c r="N59" s="21"/>
+        <v>786</v>
+      </c>
+      <c r="K59" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L59" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M59" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N59" s="21" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4186,26 +4186,50 @@
       </c>
     </row>
     <row r="60" spans="1:14">
-      <c r="A60" s="18"/>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="19"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="18">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="19">
+        <v>470</v>
+      </c>
+      <c r="C60" s="19">
+        <v>23</v>
+      </c>
+      <c r="D60" s="19">
+        <v>120</v>
+      </c>
+      <c r="E60" s="19">
+        <v>23</v>
+      </c>
+      <c r="F60" s="19">
+        <v>0</v>
+      </c>
+      <c r="G60" s="19">
+        <v>0</v>
+      </c>
+      <c r="H60" s="19">
+        <v>446</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1082</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="20"/>
-      <c r="L60" s="20"/>
-      <c r="M60" s="20"/>
-      <c r="N60" s="21"/>
+        <v>358</v>
+      </c>
+      <c r="K60" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L60" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M60" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N60" s="21" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4232,26 +4232,50 @@
       </c>
     </row>
     <row r="61" spans="1:14">
-      <c r="A61" s="18"/>
-      <c r="B61" s="19"/>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="18">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="19">
+        <v>460</v>
+      </c>
+      <c r="C61" s="19">
+        <v>12</v>
+      </c>
+      <c r="D61" s="19">
+        <v>232</v>
+      </c>
+      <c r="E61" s="19">
+        <v>12</v>
+      </c>
+      <c r="F61" s="19">
+        <v>0</v>
+      </c>
+      <c r="G61" s="19">
+        <v>0</v>
+      </c>
+      <c r="H61" s="19">
+        <v>454</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="20"/>
-      <c r="L61" s="20"/>
-      <c r="M61" s="20"/>
-      <c r="N61" s="21"/>
+        <v>270</v>
+      </c>
+      <c r="K61" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L61" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="M61" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N61" s="21" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4278,26 +4278,48 @@
       </c>
     </row>
     <row r="62" spans="1:14">
-      <c r="A62" s="18"/>
+      <c r="A62" s="18">
+        <v>46312</v>
+      </c>
       <c r="B62" s="19"/>
-      <c r="C62" s="19"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="19"/>
-      <c r="F62" s="19"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="19"/>
-      <c r="I62" s="15" t="str">
+      <c r="C62" s="19">
+        <v>32</v>
+      </c>
+      <c r="D62" s="19">
+        <v>247</v>
+      </c>
+      <c r="E62" s="19">
+        <v>32</v>
+      </c>
+      <c r="F62" s="19">
+        <v>0</v>
+      </c>
+      <c r="G62" s="19">
+        <v>0</v>
+      </c>
+      <c r="H62" s="19">
+        <v>643</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>954</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="20"/>
-      <c r="L62" s="20"/>
-      <c r="M62" s="20"/>
-      <c r="N62" s="21"/>
+        <v>486</v>
+      </c>
+      <c r="K62" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L62" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M62" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N62" s="21" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6300" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4322,48 +4322,96 @@
       </c>
     </row>
     <row r="63" spans="1:14">
-      <c r="A63" s="18"/>
-      <c r="B63" s="19"/>
-      <c r="C63" s="19"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="19"/>
-      <c r="F63" s="19"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="19"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="18">
+        <v>46313</v>
+      </c>
+      <c r="B63" s="19">
+        <v>469</v>
+      </c>
+      <c r="C63" s="19">
+        <v>12</v>
+      </c>
+      <c r="D63" s="19">
+        <v>232</v>
+      </c>
+      <c r="E63" s="19">
+        <v>45</v>
+      </c>
+      <c r="F63" s="19">
+        <v>0</v>
+      </c>
+      <c r="G63" s="19">
+        <v>0</v>
+      </c>
+      <c r="H63" s="19">
+        <v>533</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1291</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="20"/>
-      <c r="L63" s="20"/>
-      <c r="M63" s="20"/>
-      <c r="N63" s="21"/>
+        <v>149</v>
+      </c>
+      <c r="K63" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L63" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M63" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N63" s="21" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="64" spans="1:14">
-      <c r="A64" s="18"/>
-      <c r="B64" s="19"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="18">
+        <v>46314</v>
+      </c>
+      <c r="B64" s="19">
+        <v>456</v>
+      </c>
+      <c r="C64" s="19">
+        <v>21</v>
+      </c>
+      <c r="D64" s="19">
+        <v>344</v>
+      </c>
+      <c r="E64" s="19">
+        <v>23</v>
+      </c>
+      <c r="F64" s="19">
+        <v>0</v>
+      </c>
+      <c r="G64" s="19">
+        <v>0</v>
+      </c>
+      <c r="H64" s="19">
+        <v>324</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>1168</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="20"/>
-      <c r="L64" s="20"/>
-      <c r="M64" s="20"/>
-      <c r="N64" s="21"/>
+        <v>272</v>
+      </c>
+      <c r="K64" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L64" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="M64" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N64" s="21" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4414,26 +4414,48 @@
       </c>
     </row>
     <row r="65" spans="1:14">
-      <c r="A65" s="18"/>
+      <c r="A65" s="18">
+        <v>46315</v>
+      </c>
       <c r="B65" s="19"/>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="15" t="str">
+      <c r="C65" s="19">
+        <v>32</v>
+      </c>
+      <c r="D65" s="19">
+        <v>137</v>
+      </c>
+      <c r="E65" s="19">
+        <v>12</v>
+      </c>
+      <c r="F65" s="19">
+        <v>0</v>
+      </c>
+      <c r="G65" s="19">
+        <v>0</v>
+      </c>
+      <c r="H65" s="19">
+        <v>434</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>615</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="20"/>
-      <c r="L65" s="20"/>
-      <c r="M65" s="20"/>
-      <c r="N65" s="21"/>
+        <v>825</v>
+      </c>
+      <c r="K65" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L65" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M65" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N65" s="21" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6300" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6300" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>irritated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bit confident </t>
   </si>
 </sst>
 </file>
@@ -4458,26 +4461,50 @@
       </c>
     </row>
     <row r="66" spans="1:14">
-      <c r="A66" s="18"/>
-      <c r="B66" s="19"/>
-      <c r="C66" s="19"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="19"/>
-      <c r="F66" s="19"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="19"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="18">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="19">
+        <v>479</v>
+      </c>
+      <c r="C66" s="19">
+        <v>23</v>
+      </c>
+      <c r="D66" s="19">
+        <v>110</v>
+      </c>
+      <c r="E66" s="19">
+        <v>16</v>
+      </c>
+      <c r="F66" s="19">
+        <v>6</v>
+      </c>
+      <c r="G66" s="19">
+        <v>4</v>
+      </c>
+      <c r="H66" s="19">
+        <v>455</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>1089</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="20"/>
-      <c r="L66" s="20"/>
-      <c r="M66" s="20"/>
-      <c r="N66" s="21"/>
+        <v>351</v>
+      </c>
+      <c r="K66" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L66" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M66" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N66" s="21" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4507,26 +4507,50 @@
       </c>
     </row>
     <row r="67" spans="1:14">
-      <c r="A67" s="18"/>
-      <c r="B67" s="19"/>
-      <c r="C67" s="19"/>
-      <c r="D67" s="19"/>
-      <c r="E67" s="19"/>
-      <c r="F67" s="19"/>
-      <c r="G67" s="19"/>
-      <c r="H67" s="19"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="18">
+        <v>46317</v>
+      </c>
+      <c r="B67" s="19">
+        <v>467</v>
+      </c>
+      <c r="C67" s="19">
+        <v>25</v>
+      </c>
+      <c r="D67" s="19">
+        <v>145</v>
+      </c>
+      <c r="E67" s="19">
+        <v>31</v>
+      </c>
+      <c r="F67" s="19">
+        <v>5</v>
+      </c>
+      <c r="G67" s="19">
+        <v>4</v>
+      </c>
+      <c r="H67" s="19">
+        <v>245</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>918</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="20"/>
-      <c r="L67" s="20"/>
-      <c r="M67" s="20"/>
-      <c r="N67" s="21"/>
+        <v>522</v>
+      </c>
+      <c r="K67" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="L67" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M67" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N67" s="21" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4159,7 +4159,7 @@
         <v>23</v>
       </c>
       <c r="F59" s="19">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="G59" s="19">
         <v>0</v>
@@ -4169,11 +4169,11 @@
       </c>
       <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v>654</v>
+        <v>888</v>
       </c>
       <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v>786</v>
+        <v>552</v>
       </c>
       <c r="K59" s="20" t="s">
         <v>57</v>
@@ -4477,7 +4477,7 @@
         <v>16</v>
       </c>
       <c r="F66" s="19">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="G66" s="19">
         <v>4</v>
@@ -4487,11 +4487,11 @@
       </c>
       <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v>1089</v>
+        <v>1283</v>
       </c>
       <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v>351</v>
+        <v>157</v>
       </c>
       <c r="K66" s="20" t="s">
         <v>57</v>
@@ -4523,7 +4523,7 @@
         <v>31</v>
       </c>
       <c r="F67" s="19">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="G67" s="19">
         <v>4</v>
@@ -4533,11 +4533,11 @@
       </c>
       <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v>918</v>
+        <v>1113</v>
       </c>
       <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v>522</v>
+        <v>327</v>
       </c>
       <c r="K67" s="20" t="s">
         <v>60</v>
@@ -4553,26 +4553,48 @@
       </c>
     </row>
     <row r="68" spans="1:14">
-      <c r="A68" s="18"/>
+      <c r="A68" s="18">
+        <v>46318</v>
+      </c>
       <c r="B68" s="19"/>
-      <c r="C68" s="19"/>
-      <c r="D68" s="19"/>
-      <c r="E68" s="19"/>
-      <c r="F68" s="19"/>
-      <c r="G68" s="19"/>
-      <c r="H68" s="19"/>
-      <c r="I68" s="15" t="str">
+      <c r="C68" s="19">
+        <v>32</v>
+      </c>
+      <c r="D68" s="19">
+        <v>110</v>
+      </c>
+      <c r="E68" s="19">
+        <v>12</v>
+      </c>
+      <c r="F68" s="19">
+        <v>200</v>
+      </c>
+      <c r="G68" s="19">
+        <v>4</v>
+      </c>
+      <c r="H68" s="19">
+        <v>643</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>997</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="20"/>
-      <c r="L68" s="20"/>
-      <c r="M68" s="20"/>
-      <c r="N68" s="21"/>
+        <v>443</v>
+      </c>
+      <c r="K68" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="L68" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M68" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N68" s="21" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4597,26 +4597,50 @@
       </c>
     </row>
     <row r="69" spans="1:14">
-      <c r="A69" s="18"/>
-      <c r="B69" s="19"/>
-      <c r="C69" s="19"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="19"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
-      <c r="H69" s="19"/>
-      <c r="I69" s="15" t="str">
+      <c r="A69" s="18">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="19">
+        <v>446</v>
+      </c>
+      <c r="C69" s="19">
+        <v>12</v>
+      </c>
+      <c r="D69" s="19">
+        <v>111</v>
+      </c>
+      <c r="E69" s="19">
+        <v>13</v>
+      </c>
+      <c r="F69" s="19">
+        <v>0</v>
+      </c>
+      <c r="G69" s="19">
+        <v>0</v>
+      </c>
+      <c r="H69" s="19">
+        <v>434</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>1016</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="20"/>
-      <c r="L69" s="20"/>
-      <c r="M69" s="20"/>
-      <c r="N69" s="21"/>
+        <v>424</v>
+      </c>
+      <c r="K69" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L69" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M69" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N69" s="21" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4643,26 +4643,50 @@
       </c>
     </row>
     <row r="70" spans="1:14">
-      <c r="A70" s="18"/>
-      <c r="B70" s="19"/>
-      <c r="C70" s="19"/>
-      <c r="D70" s="19"/>
-      <c r="E70" s="19"/>
-      <c r="F70" s="19"/>
-      <c r="G70" s="19"/>
-      <c r="H70" s="19"/>
-      <c r="I70" s="15" t="str">
+      <c r="A70" s="18">
+        <v>46320</v>
+      </c>
+      <c r="B70" s="19">
+        <v>467</v>
+      </c>
+      <c r="C70" s="19">
+        <v>15</v>
+      </c>
+      <c r="D70" s="19">
+        <v>30</v>
+      </c>
+      <c r="E70" s="19">
+        <v>10</v>
+      </c>
+      <c r="F70" s="19">
+        <v>0</v>
+      </c>
+      <c r="G70" s="19">
+        <v>0</v>
+      </c>
+      <c r="H70" s="19">
+        <v>575</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>1097</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="20"/>
-      <c r="L70" s="20"/>
-      <c r="M70" s="20"/>
-      <c r="N70" s="21"/>
+        <v>343</v>
+      </c>
+      <c r="K70" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L70" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M70" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N70" s="21" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4689,26 +4689,50 @@
       </c>
     </row>
     <row r="71" spans="1:14">
-      <c r="A71" s="18"/>
-      <c r="B71" s="19"/>
-      <c r="C71" s="19"/>
-      <c r="D71" s="19"/>
-      <c r="E71" s="19"/>
-      <c r="F71" s="19"/>
-      <c r="G71" s="19"/>
-      <c r="H71" s="19"/>
-      <c r="I71" s="15" t="str">
+      <c r="A71" s="18">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="19">
+        <v>450</v>
+      </c>
+      <c r="C71" s="19">
+        <v>14</v>
+      </c>
+      <c r="D71" s="19">
+        <v>30</v>
+      </c>
+      <c r="E71" s="19">
+        <v>12</v>
+      </c>
+      <c r="F71" s="19">
+        <v>0</v>
+      </c>
+      <c r="G71" s="19">
+        <v>0</v>
+      </c>
+      <c r="H71" s="19">
+        <v>644</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="20"/>
-      <c r="L71" s="20"/>
-      <c r="M71" s="20"/>
-      <c r="N71" s="21"/>
+        <v>290</v>
+      </c>
+      <c r="K71" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L71" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M71" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N71" s="21" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6300" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4735,26 +4735,50 @@
       </c>
     </row>
     <row r="72" spans="1:14">
-      <c r="A72" s="18"/>
-      <c r="B72" s="19"/>
-      <c r="C72" s="19"/>
-      <c r="D72" s="19"/>
-      <c r="E72" s="19"/>
-      <c r="F72" s="19"/>
-      <c r="G72" s="19"/>
-      <c r="H72" s="19"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="18">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="19">
+        <v>480</v>
+      </c>
+      <c r="C72" s="19">
+        <v>10</v>
+      </c>
+      <c r="D72" s="19">
+        <v>23</v>
+      </c>
+      <c r="E72" s="19">
+        <v>30</v>
+      </c>
+      <c r="F72" s="19">
+        <v>250</v>
+      </c>
+      <c r="G72" s="19">
+        <v>5</v>
+      </c>
+      <c r="H72" s="19">
+        <v>454</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>1247</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="20"/>
-      <c r="L72" s="20"/>
-      <c r="M72" s="20"/>
-      <c r="N72" s="21"/>
+        <v>193</v>
+      </c>
+      <c r="K72" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L72" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="M72" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N72" s="21" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6300" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4781,26 +4781,50 @@
       </c>
     </row>
     <row r="73" spans="1:14">
-      <c r="A73" s="18"/>
-      <c r="B73" s="19"/>
-      <c r="C73" s="19"/>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="19"/>
-      <c r="H73" s="19"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="18">
+        <v>46323</v>
+      </c>
+      <c r="B73" s="19">
+        <v>469</v>
+      </c>
+      <c r="C73" s="19">
+        <v>12</v>
+      </c>
+      <c r="D73" s="19">
+        <v>43</v>
+      </c>
+      <c r="E73" s="19">
+        <v>15</v>
+      </c>
+      <c r="F73" s="19">
+        <v>100</v>
+      </c>
+      <c r="G73" s="19">
+        <v>2</v>
+      </c>
+      <c r="H73" s="19">
+        <v>644</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>1283</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="20"/>
-      <c r="L73" s="20"/>
-      <c r="M73" s="20"/>
-      <c r="N73" s="21"/>
+        <v>157</v>
+      </c>
+      <c r="K73" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L73" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M73" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N73" s="21" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4827,26 +4827,50 @@
       </c>
     </row>
     <row r="74" spans="1:14">
-      <c r="A74" s="18"/>
-      <c r="B74" s="19"/>
-      <c r="C74" s="19"/>
-      <c r="D74" s="19"/>
-      <c r="E74" s="19"/>
-      <c r="F74" s="19"/>
-      <c r="G74" s="19"/>
-      <c r="H74" s="19"/>
-      <c r="I74" s="15" t="str">
+      <c r="A74" s="18">
+        <v>46324</v>
+      </c>
+      <c r="B74" s="19">
+        <v>456</v>
+      </c>
+      <c r="C74" s="19">
+        <v>40</v>
+      </c>
+      <c r="D74" s="19">
+        <v>30</v>
+      </c>
+      <c r="E74" s="19">
+        <v>12</v>
+      </c>
+      <c r="F74" s="19">
+        <v>200</v>
+      </c>
+      <c r="G74" s="19">
+        <v>4</v>
+      </c>
+      <c r="H74" s="19">
+        <v>654</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>1392</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="20"/>
-      <c r="L74" s="20"/>
-      <c r="M74" s="20"/>
-      <c r="N74" s="21"/>
+        <v>48</v>
+      </c>
+      <c r="K74" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L74" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="M74" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N74" s="21" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6300" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4873,26 +4873,50 @@
       </c>
     </row>
     <row r="75" spans="1:14">
-      <c r="A75" s="18"/>
-      <c r="B75" s="19"/>
-      <c r="C75" s="19"/>
-      <c r="D75" s="19"/>
-      <c r="E75" s="19"/>
-      <c r="F75" s="19"/>
-      <c r="G75" s="19"/>
-      <c r="H75" s="19"/>
-      <c r="I75" s="15" t="str">
+      <c r="A75" s="18">
+        <v>46325</v>
+      </c>
+      <c r="B75" s="19">
+        <v>480</v>
+      </c>
+      <c r="C75" s="19">
+        <v>23</v>
+      </c>
+      <c r="D75" s="19">
+        <v>45</v>
+      </c>
+      <c r="E75" s="19">
+        <v>12</v>
+      </c>
+      <c r="F75" s="19">
+        <v>200</v>
+      </c>
+      <c r="G75" s="19">
+        <v>4</v>
+      </c>
+      <c r="H75" s="19">
+        <v>456</v>
+      </c>
+      <c r="I75" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
+        <v>1216</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="20"/>
-      <c r="L75" s="20"/>
-      <c r="M75" s="20"/>
-      <c r="N75" s="21"/>
+        <v>224</v>
+      </c>
+      <c r="K75" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L75" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M75" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N75" s="21" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6300" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4919,26 +4919,50 @@
       </c>
     </row>
     <row r="76" spans="1:14">
-      <c r="A76" s="18"/>
-      <c r="B76" s="19"/>
-      <c r="C76" s="19"/>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="19"/>
-      <c r="G76" s="19"/>
-      <c r="H76" s="19"/>
-      <c r="I76" s="15" t="str">
+      <c r="A76" s="18">
+        <v>46326</v>
+      </c>
+      <c r="B76" s="19">
+        <v>489</v>
+      </c>
+      <c r="C76" s="19">
+        <v>12</v>
+      </c>
+      <c r="D76" s="19">
+        <v>23</v>
+      </c>
+      <c r="E76" s="19">
+        <v>13</v>
+      </c>
+      <c r="F76" s="19">
+        <v>0</v>
+      </c>
+      <c r="G76" s="19">
+        <v>0</v>
+      </c>
+      <c r="H76" s="19">
+        <v>567</v>
+      </c>
+      <c r="I76" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
+        <v>1104</v>
+      </c>
+      <c r="J76" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="20"/>
-      <c r="L76" s="20"/>
-      <c r="M76" s="20"/>
-      <c r="N76" s="21"/>
+        <v>336</v>
+      </c>
+      <c r="K76" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L76" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M76" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N76" s="21" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="18"/>
